--- a/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_2.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_8/231FL_10A_2.xlsx
@@ -7738,7 +7738,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7857,7 +7857,7 @@
         <v>0</v>
       </c>
       <c r="D11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>1</v>
